--- a/data/nzd0604/nzd0604.xlsx
+++ b/data/nzd0604/nzd0604.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M355"/>
+  <dimension ref="A1:M356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16302,7 +16302,7 @@
         <v>353.1</v>
       </c>
       <c r="J355" t="n">
-        <v>293.55</v>
+        <v>270.9</v>
       </c>
       <c r="K355" t="n">
         <v>355.04</v>
@@ -16313,6 +16313,51 @@
       <c r="M355" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>295.79</v>
+      </c>
+      <c r="C356" t="n">
+        <v>261.32</v>
+      </c>
+      <c r="D356" t="n">
+        <v>234.76</v>
+      </c>
+      <c r="E356" t="n">
+        <v>233.78</v>
+      </c>
+      <c r="F356" t="n">
+        <v>229.07</v>
+      </c>
+      <c r="G356" t="n">
+        <v>259.54</v>
+      </c>
+      <c r="H356" t="n">
+        <v>293.95</v>
+      </c>
+      <c r="I356" t="n">
+        <v>353.1</v>
+      </c>
+      <c r="J356" t="n">
+        <v>205.54</v>
+      </c>
+      <c r="K356" t="n">
+        <v>355.04</v>
+      </c>
+      <c r="L356" t="n">
+        <v>307.39</v>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -16327,7 +16372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B388"/>
+  <dimension ref="A1:B389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20210,6 +20255,16 @@
       </c>
       <c r="B388" t="n">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>-0.77</v>
       </c>
     </row>
   </sheetData>
@@ -20372,28 +20427,28 @@
         <v>0.0208</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7391952741135114</v>
+        <v>0.733501401744563</v>
       </c>
       <c r="J2" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K2" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1435335064517969</v>
+        <v>0.142112902728496</v>
       </c>
       <c r="M2" t="n">
-        <v>9.831414091006028</v>
+        <v>9.833176903021824</v>
       </c>
       <c r="N2" t="n">
-        <v>180.2714950372057</v>
+        <v>180.0820392631556</v>
       </c>
       <c r="O2" t="n">
-        <v>13.42652207525112</v>
+        <v>13.41946493952555</v>
       </c>
       <c r="P2" t="n">
-        <v>287.0572547429207</v>
+        <v>287.1169372449874</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20444,28 +20499,28 @@
         <v>0.0364</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2186620779670914</v>
+        <v>0.223577955985499</v>
       </c>
       <c r="J3" t="n">
+        <v>355</v>
+      </c>
+      <c r="K3" t="n">
         <v>354</v>
       </c>
-      <c r="K3" t="n">
-        <v>353</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.02367877513456573</v>
+        <v>0.02481190855232041</v>
       </c>
       <c r="M3" t="n">
-        <v>7.732058889210694</v>
+        <v>7.737066099842897</v>
       </c>
       <c r="N3" t="n">
-        <v>109.0023705677528</v>
+        <v>108.9320311148407</v>
       </c>
       <c r="O3" t="n">
-        <v>10.44042003789851</v>
+        <v>10.43705088206629</v>
       </c>
       <c r="P3" t="n">
-        <v>246.3705466975464</v>
+        <v>246.3189676390571</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20516,28 +20571,28 @@
         <v>0.0694</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3951566162249243</v>
+        <v>0.3936653889616068</v>
       </c>
       <c r="J4" t="n">
+        <v>355</v>
+      </c>
+      <c r="K4" t="n">
         <v>354</v>
       </c>
-      <c r="K4" t="n">
-        <v>353</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.08936043607429445</v>
+        <v>0.08918263227333711</v>
       </c>
       <c r="M4" t="n">
-        <v>6.96866794330621</v>
+        <v>6.953993423811169</v>
       </c>
       <c r="N4" t="n">
-        <v>87.98228861394126</v>
+        <v>87.75561306042231</v>
       </c>
       <c r="O4" t="n">
-        <v>9.379887452093509</v>
+        <v>9.367796595807485</v>
       </c>
       <c r="P4" t="n">
-        <v>227.1777510088581</v>
+        <v>227.1933974707816</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20588,28 +20643,28 @@
         <v>0.1048</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1837486599250925</v>
+        <v>0.1844832326959961</v>
       </c>
       <c r="J5" t="n">
+        <v>355</v>
+      </c>
+      <c r="K5" t="n">
         <v>354</v>
       </c>
-      <c r="K5" t="n">
-        <v>353</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.02528526454142843</v>
+        <v>0.02562086313244316</v>
       </c>
       <c r="M5" t="n">
-        <v>6.434916166160527</v>
+        <v>6.420205301789061</v>
       </c>
       <c r="N5" t="n">
-        <v>71.96376795101686</v>
+        <v>71.76578530216932</v>
       </c>
       <c r="O5" t="n">
-        <v>8.483146111615481</v>
+        <v>8.471468898731159</v>
       </c>
       <c r="P5" t="n">
-        <v>227.5820683619478</v>
+        <v>227.5743609754396</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20660,28 +20715,28 @@
         <v>0.0842</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3811329473725728</v>
+        <v>0.3833644841368</v>
       </c>
       <c r="J6" t="n">
+        <v>355</v>
+      </c>
+      <c r="K6" t="n">
         <v>354</v>
       </c>
-      <c r="K6" t="n">
-        <v>353</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1024718872475119</v>
+        <v>0.1040089263554256</v>
       </c>
       <c r="M6" t="n">
-        <v>6.349574737676263</v>
+        <v>6.340454210847013</v>
       </c>
       <c r="N6" t="n">
-        <v>70.34800992249832</v>
+        <v>70.19824319132385</v>
       </c>
       <c r="O6" t="n">
-        <v>8.387372051035909</v>
+        <v>8.378439185870114</v>
       </c>
       <c r="P6" t="n">
-        <v>214.883113634705</v>
+        <v>214.8596995945576</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20732,28 +20787,28 @@
         <v>0.0299</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4752368394061177</v>
+        <v>0.4815385970203899</v>
       </c>
       <c r="J7" t="n">
+        <v>355</v>
+      </c>
+      <c r="K7" t="n">
         <v>354</v>
       </c>
-      <c r="K7" t="n">
-        <v>353</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01712619410104732</v>
+        <v>0.0176632378325513</v>
       </c>
       <c r="M7" t="n">
-        <v>20.15868314474691</v>
+        <v>20.13023110245499</v>
       </c>
       <c r="N7" t="n">
-        <v>718.0561662707275</v>
+        <v>716.4190022076964</v>
       </c>
       <c r="O7" t="n">
-        <v>26.7965700467565</v>
+        <v>26.76600459926166</v>
       </c>
       <c r="P7" t="n">
-        <v>235.2371398127093</v>
+        <v>235.1711135532352</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -20804,28 +20859,28 @@
         <v>0.0154</v>
       </c>
       <c r="I8" t="n">
-        <v>1.617347844693211</v>
+        <v>1.599296739080855</v>
       </c>
       <c r="J8" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K8" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09916057896304209</v>
+        <v>0.09744955137151046</v>
       </c>
       <c r="M8" t="n">
-        <v>27.20144156519658</v>
+        <v>27.18506629850214</v>
       </c>
       <c r="N8" t="n">
-        <v>1280.384719360103</v>
+        <v>1279.7659273427</v>
       </c>
       <c r="O8" t="n">
-        <v>35.78246385256475</v>
+        <v>35.77381622559577</v>
       </c>
       <c r="P8" t="n">
-        <v>284.3197423481559</v>
+        <v>284.5147042895011</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -20876,28 +20931,28 @@
         <v>0.0114</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2005300066960448</v>
+        <v>-0.1883626894511098</v>
       </c>
       <c r="J9" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K9" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004485587768528809</v>
+        <v>0.00397096239360506</v>
       </c>
       <c r="M9" t="n">
-        <v>16.60707115327322</v>
+        <v>16.63850462012749</v>
       </c>
       <c r="N9" t="n">
-        <v>481.4820019564337</v>
+        <v>481.4994433158238</v>
       </c>
       <c r="O9" t="n">
-        <v>21.94269814668273</v>
+        <v>21.9430955727724</v>
       </c>
       <c r="P9" t="n">
-        <v>336.1862441791694</v>
+        <v>336.0563097092529</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -20948,28 +21003,28 @@
         <v>0.0157</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4818828165982695</v>
+        <v>0.4166724304629625</v>
       </c>
       <c r="J10" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K10" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02961524814580563</v>
+        <v>0.02097278340624142</v>
       </c>
       <c r="M10" t="n">
-        <v>14.7824358800873</v>
+        <v>15.11835439139509</v>
       </c>
       <c r="N10" t="n">
-        <v>412.4109821662198</v>
+        <v>440.5081487455258</v>
       </c>
       <c r="O10" t="n">
-        <v>20.30790442577027</v>
+        <v>20.9882859887492</v>
       </c>
       <c r="P10" t="n">
-        <v>289.6991140319536</v>
+        <v>290.3952047829876</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21020,28 +21075,28 @@
         <v>0.0103</v>
       </c>
       <c r="I11" t="n">
-        <v>3.734129631855753</v>
+        <v>3.713408780847942</v>
       </c>
       <c r="J11" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K11" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3343836652836349</v>
+        <v>0.3326142973716282</v>
       </c>
       <c r="M11" t="n">
-        <v>31.40967111577123</v>
+        <v>31.39827363705776</v>
       </c>
       <c r="N11" t="n">
-        <v>1475.331263598977</v>
+        <v>1474.829983639446</v>
       </c>
       <c r="O11" t="n">
-        <v>38.41004118194846</v>
+        <v>38.40351525107365</v>
       </c>
       <c r="P11" t="n">
-        <v>293.304519853945</v>
+        <v>293.5294877154543</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21092,28 +21147,28 @@
         <v>0.0174</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2248289622402967</v>
+        <v>-0.2146908212631624</v>
       </c>
       <c r="J12" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K12" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L12" t="n">
-        <v>0.006238584310208295</v>
+        <v>0.005710704148561674</v>
       </c>
       <c r="M12" t="n">
-        <v>15.0947991627038</v>
+        <v>15.08755498098868</v>
       </c>
       <c r="N12" t="n">
-        <v>447.180008421301</v>
+        <v>446.9295014522966</v>
       </c>
       <c r="O12" t="n">
-        <v>21.14663113645531</v>
+        <v>21.14070721268086</v>
       </c>
       <c r="P12" t="n">
-        <v>294.2683871096837</v>
+        <v>294.1622586161774</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -21151,7 +21206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M355"/>
+  <dimension ref="A1:M356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44696,7 +44751,7 @@
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>-36.94580263738706,175.17137032094848</t>
+          <t>-36.94595499769395,175.1715394899724</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
@@ -44712,6 +44767,73 @@
       <c r="M355" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>-36.94720861043213,175.16578938222685</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>-36.94765516290248,175.16630727829008</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-36.94784750838027,175.16718071485445</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-36.947781406440996,175.1680754597869</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>-36.9475639334998,175.16880106093942</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>-36.947013750589896,175.16947446082176</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>-36.94643268375853,175.1701147774808</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>-36.945641819425504,175.17064062790104</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>-36.94639465490332,175.17202765656992</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>-36.94556204402631,175.170792603786</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>-36.94502317988301,175.17141122791992</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0604/nzd0604.xlsx
+++ b/data/nzd0604/nzd0604.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M356"/>
+  <dimension ref="A1:M360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16335,7 +16335,7 @@
         <v>233.78</v>
       </c>
       <c r="F356" t="n">
-        <v>229.07</v>
+        <v>225.09</v>
       </c>
       <c r="G356" t="n">
         <v>259.54</v>
@@ -16347,7 +16347,7 @@
         <v>353.1</v>
       </c>
       <c r="J356" t="n">
-        <v>205.54</v>
+        <v>270.9</v>
       </c>
       <c r="K356" t="n">
         <v>355.04</v>
@@ -16358,6 +16358,184 @@
       <c r="M356" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>296.32</v>
+      </c>
+      <c r="C357" t="n">
+        <v>258.31</v>
+      </c>
+      <c r="D357" t="n">
+        <v>235.9</v>
+      </c>
+      <c r="E357" t="n">
+        <v>236.03</v>
+      </c>
+      <c r="F357" t="n">
+        <v>225.83</v>
+      </c>
+      <c r="G357" t="n">
+        <v>256.98</v>
+      </c>
+      <c r="H357" t="n">
+        <v>295.48</v>
+      </c>
+      <c r="I357" t="n">
+        <v>352.62</v>
+      </c>
+      <c r="J357" t="n">
+        <v>270.9</v>
+      </c>
+      <c r="K357" t="n">
+        <v>358.74</v>
+      </c>
+      <c r="L357" t="n">
+        <v>304.61</v>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>301.47</v>
+      </c>
+      <c r="C358" t="n">
+        <v>259.32</v>
+      </c>
+      <c r="D358" t="n">
+        <v>239.19</v>
+      </c>
+      <c r="E358" t="n">
+        <v>241.38</v>
+      </c>
+      <c r="F358" t="n">
+        <v>230.04</v>
+      </c>
+      <c r="G358" t="n">
+        <v>263.66</v>
+      </c>
+      <c r="H358" t="n">
+        <v>302.62</v>
+      </c>
+      <c r="I358" t="n">
+        <v>363.58</v>
+      </c>
+      <c r="J358" t="inlineStr"/>
+      <c r="K358" t="n">
+        <v>361.59</v>
+      </c>
+      <c r="L358" t="n">
+        <v>309.58</v>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>301.21</v>
+      </c>
+      <c r="C359" t="n">
+        <v>258.07</v>
+      </c>
+      <c r="D359" t="n">
+        <v>239</v>
+      </c>
+      <c r="E359" t="n">
+        <v>240.89</v>
+      </c>
+      <c r="F359" t="n">
+        <v>230.09</v>
+      </c>
+      <c r="G359" t="n">
+        <v>263.66</v>
+      </c>
+      <c r="H359" t="n">
+        <v>295.66</v>
+      </c>
+      <c r="I359" t="n">
+        <v>359.11</v>
+      </c>
+      <c r="J359" t="n">
+        <v>257.34</v>
+      </c>
+      <c r="K359" t="n">
+        <v>361.59</v>
+      </c>
+      <c r="L359" t="n">
+        <v>302.92</v>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>299.82</v>
+      </c>
+      <c r="C360" t="n">
+        <v>258.07</v>
+      </c>
+      <c r="D360" t="n">
+        <v>236.54</v>
+      </c>
+      <c r="E360" t="n">
+        <v>238.76</v>
+      </c>
+      <c r="F360" t="n">
+        <v>227.7</v>
+      </c>
+      <c r="G360" t="n">
+        <v>291.05</v>
+      </c>
+      <c r="H360" t="n">
+        <v>296.21</v>
+      </c>
+      <c r="I360" t="n">
+        <v>359.11</v>
+      </c>
+      <c r="J360" t="n">
+        <v>257.34</v>
+      </c>
+      <c r="K360" t="n">
+        <v>384.1</v>
+      </c>
+      <c r="L360" t="n">
+        <v>302.92</v>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -16372,7 +16550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B389"/>
+  <dimension ref="A1:B393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20265,6 +20443,46 @@
       </c>
       <c r="B389" t="n">
         <v>-0.77</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>-0.92</v>
       </c>
     </row>
   </sheetData>
@@ -20427,28 +20645,28 @@
         <v>0.0208</v>
       </c>
       <c r="I2" t="n">
-        <v>0.733501401744563</v>
+        <v>0.7195148507915159</v>
       </c>
       <c r="J2" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K2" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="L2" t="n">
-        <v>0.142112902728496</v>
+        <v>0.1397783133645649</v>
       </c>
       <c r="M2" t="n">
-        <v>9.833176903021824</v>
+        <v>9.794822058835505</v>
       </c>
       <c r="N2" t="n">
-        <v>180.0820392631556</v>
+        <v>178.6104983869054</v>
       </c>
       <c r="O2" t="n">
-        <v>13.41946493952555</v>
+        <v>13.36452387430639</v>
       </c>
       <c r="P2" t="n">
-        <v>287.1169372449874</v>
+        <v>287.2640486900457</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20499,28 +20717,28 @@
         <v>0.0364</v>
       </c>
       <c r="I3" t="n">
-        <v>0.223577955985499</v>
+        <v>0.2365435423599387</v>
       </c>
       <c r="J3" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K3" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02481190855232041</v>
+        <v>0.02818749080167382</v>
       </c>
       <c r="M3" t="n">
-        <v>7.737066099842897</v>
+        <v>7.722520030978619</v>
       </c>
       <c r="N3" t="n">
-        <v>108.9320311148407</v>
+        <v>108.1378403233545</v>
       </c>
       <c r="O3" t="n">
-        <v>10.43705088206629</v>
+        <v>10.39893457635707</v>
       </c>
       <c r="P3" t="n">
-        <v>246.3189676390571</v>
+        <v>246.1824357966589</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20571,28 +20789,28 @@
         <v>0.0694</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3936653889616068</v>
+        <v>0.3938643435893434</v>
       </c>
       <c r="J4" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K4" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08918263227333711</v>
+        <v>0.09106311551702795</v>
       </c>
       <c r="M4" t="n">
-        <v>6.953993423811169</v>
+        <v>6.892733301148339</v>
       </c>
       <c r="N4" t="n">
-        <v>87.75561306042231</v>
+        <v>86.79885305646872</v>
       </c>
       <c r="O4" t="n">
-        <v>9.367796595807485</v>
+        <v>9.316590205459759</v>
       </c>
       <c r="P4" t="n">
-        <v>227.1933974707816</v>
+        <v>227.1912975426933</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20643,28 +20861,28 @@
         <v>0.1048</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1844832326959961</v>
+        <v>0.1987027437004286</v>
       </c>
       <c r="J5" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K5" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02562086313244316</v>
+        <v>0.03001811707076507</v>
       </c>
       <c r="M5" t="n">
-        <v>6.420205301789061</v>
+        <v>6.415813262184981</v>
       </c>
       <c r="N5" t="n">
-        <v>71.76578530216932</v>
+        <v>71.51832511836568</v>
       </c>
       <c r="O5" t="n">
-        <v>8.471468898731159</v>
+        <v>8.456850780187958</v>
       </c>
       <c r="P5" t="n">
-        <v>227.5743609754396</v>
+        <v>227.4245959745948</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20715,28 +20933,28 @@
         <v>0.0842</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3833644841368</v>
+        <v>0.3885101517069585</v>
       </c>
       <c r="J6" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K6" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1040089263554256</v>
+        <v>0.1084859901607212</v>
       </c>
       <c r="M6" t="n">
-        <v>6.340454210847013</v>
+        <v>6.290239577044399</v>
       </c>
       <c r="N6" t="n">
-        <v>70.19824319132385</v>
+        <v>69.53263529597294</v>
       </c>
       <c r="O6" t="n">
-        <v>8.378439185870114</v>
+        <v>8.338623105523654</v>
       </c>
       <c r="P6" t="n">
-        <v>214.8596995945576</v>
+        <v>214.8054136787718</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20787,28 +21005,28 @@
         <v>0.0299</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4815385970203899</v>
+        <v>0.5251967682736339</v>
       </c>
       <c r="J7" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K7" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0176632378325513</v>
+        <v>0.02120547558441799</v>
       </c>
       <c r="M7" t="n">
-        <v>20.13023110245499</v>
+        <v>20.09908988410617</v>
       </c>
       <c r="N7" t="n">
-        <v>716.4190022076964</v>
+        <v>715.0898951121762</v>
       </c>
       <c r="O7" t="n">
-        <v>26.76600459926166</v>
+        <v>26.74116480470094</v>
       </c>
       <c r="P7" t="n">
-        <v>235.1711135532352</v>
+        <v>234.7117103135923</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -20859,28 +21077,28 @@
         <v>0.0154</v>
       </c>
       <c r="I8" t="n">
-        <v>1.599296739080855</v>
+        <v>1.536875528775295</v>
       </c>
       <c r="J8" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K8" t="n">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09744955137151046</v>
+        <v>0.09187094860213885</v>
       </c>
       <c r="M8" t="n">
-        <v>27.18506629850214</v>
+        <v>27.09096425547839</v>
       </c>
       <c r="N8" t="n">
-        <v>1279.7659273427</v>
+        <v>1274.552039020806</v>
       </c>
       <c r="O8" t="n">
-        <v>35.77381622559577</v>
+        <v>35.70086888327518</v>
       </c>
       <c r="P8" t="n">
-        <v>284.5147042895011</v>
+        <v>285.1914065207268</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -20931,28 +21149,28 @@
         <v>0.0114</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1883626894511098</v>
+        <v>-0.1295621066178235</v>
       </c>
       <c r="J9" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K9" t="n">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00397096239360506</v>
+        <v>0.001891958514661285</v>
       </c>
       <c r="M9" t="n">
-        <v>16.63850462012749</v>
+        <v>16.83108419003631</v>
       </c>
       <c r="N9" t="n">
-        <v>481.4994433158238</v>
+        <v>484.5058399336079</v>
       </c>
       <c r="O9" t="n">
-        <v>21.9430955727724</v>
+        <v>22.01149335991559</v>
       </c>
       <c r="P9" t="n">
-        <v>336.0563097092529</v>
+        <v>335.4260790455842</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21003,28 +21221,28 @@
         <v>0.0157</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4166724304629625</v>
+        <v>0.3878243367353805</v>
       </c>
       <c r="J10" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K10" t="n">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02097278340624142</v>
+        <v>0.01894655445239546</v>
       </c>
       <c r="M10" t="n">
-        <v>15.11835439139509</v>
+        <v>15.16088182764903</v>
       </c>
       <c r="N10" t="n">
-        <v>440.5081487455258</v>
+        <v>426.8226420020229</v>
       </c>
       <c r="O10" t="n">
-        <v>20.9882859887492</v>
+        <v>20.65968639650716</v>
       </c>
       <c r="P10" t="n">
-        <v>290.3952047829876</v>
+        <v>290.7060989642025</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21075,28 +21293,28 @@
         <v>0.0103</v>
       </c>
       <c r="I11" t="n">
-        <v>3.713408780847942</v>
+        <v>3.658336348861045</v>
       </c>
       <c r="J11" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K11" t="n">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3326142973716282</v>
+        <v>0.3298325101130591</v>
       </c>
       <c r="M11" t="n">
-        <v>31.39827363705776</v>
+        <v>31.24585732501145</v>
       </c>
       <c r="N11" t="n">
-        <v>1474.829983639446</v>
+        <v>1465.639596262703</v>
       </c>
       <c r="O11" t="n">
-        <v>38.40351525107365</v>
+        <v>38.28367271125777</v>
       </c>
       <c r="P11" t="n">
-        <v>293.5294877154543</v>
+        <v>294.1293376659748</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21147,28 +21365,28 @@
         <v>0.0174</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2146908212631624</v>
+        <v>-0.1804290549097245</v>
       </c>
       <c r="J12" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K12" t="n">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L12" t="n">
-        <v>0.005710704148561674</v>
+        <v>0.004102361302048108</v>
       </c>
       <c r="M12" t="n">
-        <v>15.08755498098868</v>
+        <v>15.04016637971053</v>
       </c>
       <c r="N12" t="n">
-        <v>446.9295014522966</v>
+        <v>444.9548234393533</v>
       </c>
       <c r="O12" t="n">
-        <v>21.14070721268086</v>
+        <v>21.09395229537019</v>
       </c>
       <c r="P12" t="n">
-        <v>294.1622586161774</v>
+        <v>293.8023100078171</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -21206,7 +21424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M356"/>
+  <dimension ref="A1:M360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44798,7 +45016,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>-36.9475639334998,175.16880106093942</t>
+          <t>-36.94759652001942,175.1688197142228</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
@@ -44818,7 +45036,7 @@
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>-36.94639465490332,175.17202765656992</t>
+          <t>-36.94595499769395,175.1715394899724</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
@@ -44834,6 +45052,270 @@
       <c r="M356" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>-36.94720406020061,175.16579118806058</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>-36.947682273965725,175.16630820370457</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-36.94783729291163,175.16717937608226</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>-36.94776124235904,175.1680728410379</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>-36.947590461219555,175.16881624602314</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>-36.94703471069425,175.169486458999</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>-36.94642023414376,175.17010740069105</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>-36.945645725177016,175.17064294218892</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>-36.94595499769395,175.1715394899724</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>-36.94555538917346,175.1707519042354</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>-36.945025846412214,175.17144225810296</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>-36.94715984568549,175.16580873530253</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>-36.947673176898,175.1663078931833</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>-36.947807811427296,175.16717551243505</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>-36.9477132966524,175.16806661424144</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>-36.947555991558545,175.16879651478993</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>-36.94698001791882,175.1694551512696</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>-36.94636213593408,175.17007297570504</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>-36.94555654383702,175.17059009934354</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>-36.94555026312852,175.17072055458596</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>-36.94502107926611,175.1713867832806</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>-36.94716207787465,175.16580784942283</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>-36.947684435645186,175.16630827749182</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>-36.94780951400544,175.16717573556352</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>-36.94771768794147,175.16806718454578</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>-36.94755558218012,175.16879628045234</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>-36.94698001791882,175.1694551512696</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>-36.94641876948316,175.17010653283359</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>-36.94559291615708,175.17061165110908</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>-36.94604621194875,175.171640767646</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>-36.94555026312852,175.17072055458596</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>-36.94502746742775,175.17146112177625</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>-36.947174011501254,175.16580311337273</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>-36.947684435645186,175.16630827749182</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>-36.947831557911655,175.16717862449102</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>-36.94773677660604,175.16806966362475</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>-36.94757515046801,175.1688074817914</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>-36.94675576105797,175.16932678069026</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>-36.94641429413129,175.17010388104714</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>-36.94559291615708,175.17061165110908</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>-36.94604621194875,175.171640767646</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>-36.94550977607033,175.1704729474884</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>-36.94502746742775,175.17146112177625</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0604/nzd0604.xlsx
+++ b/data/nzd0604/nzd0604.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M360"/>
+  <dimension ref="A1:M362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16522,18 +16522,108 @@
         <v>296.21</v>
       </c>
       <c r="I360" t="n">
-        <v>359.11</v>
+        <v>373.07</v>
       </c>
       <c r="J360" t="n">
-        <v>257.34</v>
+        <v>370.17</v>
       </c>
       <c r="K360" t="n">
-        <v>384.1</v>
+        <v>361.59</v>
       </c>
       <c r="L360" t="n">
-        <v>302.92</v>
+        <v>310.55</v>
       </c>
       <c r="M360" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>301.97</v>
+      </c>
+      <c r="C361" t="n">
+        <v>271.01</v>
+      </c>
+      <c r="D361" t="n">
+        <v>234.41</v>
+      </c>
+      <c r="E361" t="n">
+        <v>236.54</v>
+      </c>
+      <c r="F361" t="n">
+        <v>225.08</v>
+      </c>
+      <c r="G361" t="n">
+        <v>316.1</v>
+      </c>
+      <c r="H361" t="n">
+        <v>296.21</v>
+      </c>
+      <c r="I361" t="n">
+        <v>383.64</v>
+      </c>
+      <c r="J361" t="n">
+        <v>407.76</v>
+      </c>
+      <c r="K361" t="n">
+        <v>360.83</v>
+      </c>
+      <c r="L361" t="n">
+        <v>312.5</v>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>305.1</v>
+      </c>
+      <c r="C362" t="n">
+        <v>285.37</v>
+      </c>
+      <c r="D362" t="n">
+        <v>231.59</v>
+      </c>
+      <c r="E362" t="n">
+        <v>236.2</v>
+      </c>
+      <c r="F362" t="n">
+        <v>222.95</v>
+      </c>
+      <c r="G362" t="n">
+        <v>337.51</v>
+      </c>
+      <c r="H362" t="n">
+        <v>315.8</v>
+      </c>
+      <c r="I362" t="n">
+        <v>388.68</v>
+      </c>
+      <c r="J362" t="n">
+        <v>407.76</v>
+      </c>
+      <c r="K362" t="n">
+        <v>381.92</v>
+      </c>
+      <c r="L362" t="n">
+        <v>313.67</v>
+      </c>
+      <c r="M362" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16550,7 +16640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B393"/>
+  <dimension ref="A1:B395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20483,6 +20573,26 @@
       </c>
       <c r="B393" t="n">
         <v>-0.92</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>-0.97</v>
       </c>
     </row>
   </sheetData>
@@ -20645,28 +20755,28 @@
         <v>0.0208</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7195148507915159</v>
+        <v>0.7166822241467752</v>
       </c>
       <c r="J2" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K2" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1397783133645649</v>
+        <v>0.1401098389054164</v>
       </c>
       <c r="M2" t="n">
-        <v>9.794822058835505</v>
+        <v>9.755158616596411</v>
       </c>
       <c r="N2" t="n">
-        <v>178.6104983869054</v>
+        <v>177.6754699731193</v>
       </c>
       <c r="O2" t="n">
-        <v>13.36452387430639</v>
+        <v>13.32949623853502</v>
       </c>
       <c r="P2" t="n">
-        <v>287.2640486900457</v>
+        <v>287.2939722755952</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20717,28 +20827,28 @@
         <v>0.0364</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2365435423599387</v>
+        <v>0.2631513577114719</v>
       </c>
       <c r="J3" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K3" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02818749080167382</v>
+        <v>0.03383409514353775</v>
       </c>
       <c r="M3" t="n">
-        <v>7.722520030978619</v>
+        <v>7.828651879900448</v>
       </c>
       <c r="N3" t="n">
-        <v>108.1378403233545</v>
+        <v>111.4470437150247</v>
       </c>
       <c r="O3" t="n">
-        <v>10.39893457635707</v>
+        <v>10.55684819039398</v>
       </c>
       <c r="P3" t="n">
-        <v>246.1824357966589</v>
+        <v>245.9008140929363</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20789,28 +20899,28 @@
         <v>0.0694</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3938643435893434</v>
+        <v>0.3891081323054241</v>
       </c>
       <c r="J4" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K4" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09106311551702795</v>
+        <v>0.08984296521093404</v>
       </c>
       <c r="M4" t="n">
-        <v>6.892733301148339</v>
+        <v>6.870875503838646</v>
       </c>
       <c r="N4" t="n">
-        <v>86.79885305646872</v>
+        <v>86.4436406958219</v>
       </c>
       <c r="O4" t="n">
-        <v>9.316590205459759</v>
+        <v>9.297507230210789</v>
       </c>
       <c r="P4" t="n">
-        <v>227.1912975426933</v>
+        <v>227.2416397146459</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20861,28 +20971,28 @@
         <v>0.1048</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1987027437004286</v>
+        <v>0.2025161634178604</v>
       </c>
       <c r="J5" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K5" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03001811707076507</v>
+        <v>0.03144489411089202</v>
       </c>
       <c r="M5" t="n">
-        <v>6.415813262184981</v>
+        <v>6.398390288584366</v>
       </c>
       <c r="N5" t="n">
-        <v>71.51832511836568</v>
+        <v>71.19569962718369</v>
       </c>
       <c r="O5" t="n">
-        <v>8.456850780187958</v>
+        <v>8.437754418515846</v>
       </c>
       <c r="P5" t="n">
-        <v>227.4245959745948</v>
+        <v>227.3842480150259</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20933,28 +21043,28 @@
         <v>0.0842</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3885101517069585</v>
+        <v>0.3874133049804891</v>
       </c>
       <c r="J6" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K6" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1084859901607212</v>
+        <v>0.1089804216006243</v>
       </c>
       <c r="M6" t="n">
-        <v>6.290239577044399</v>
+        <v>6.262682399031624</v>
       </c>
       <c r="N6" t="n">
-        <v>69.53263529597294</v>
+        <v>69.15888897813402</v>
       </c>
       <c r="O6" t="n">
-        <v>8.338623105523654</v>
+        <v>8.316182355993284</v>
       </c>
       <c r="P6" t="n">
-        <v>214.8054136787718</v>
+        <v>214.8170319311224</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21005,28 +21115,28 @@
         <v>0.0299</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5251967682736339</v>
+        <v>0.6058918736595098</v>
       </c>
       <c r="J7" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K7" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02120547558441799</v>
+        <v>0.02706567238118696</v>
       </c>
       <c r="M7" t="n">
-        <v>20.09908988410617</v>
+        <v>20.3531338334902</v>
       </c>
       <c r="N7" t="n">
-        <v>715.0898951121762</v>
+        <v>745.1741927935499</v>
       </c>
       <c r="O7" t="n">
-        <v>26.74116480470094</v>
+        <v>27.2978789064929</v>
       </c>
       <c r="P7" t="n">
-        <v>234.7117103135923</v>
+        <v>233.8589494304905</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21077,28 +21187,28 @@
         <v>0.0154</v>
       </c>
       <c r="I8" t="n">
-        <v>1.536875528775295</v>
+        <v>1.515826127209858</v>
       </c>
       <c r="J8" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K8" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09187094860213885</v>
+        <v>0.09030774499599592</v>
       </c>
       <c r="M8" t="n">
-        <v>27.09096425547839</v>
+        <v>27.00909604598472</v>
       </c>
       <c r="N8" t="n">
-        <v>1274.552039020806</v>
+        <v>1269.980875505599</v>
       </c>
       <c r="O8" t="n">
-        <v>35.70086888327518</v>
+        <v>35.63679103827391</v>
       </c>
       <c r="P8" t="n">
-        <v>285.1914065207268</v>
+        <v>285.4205768217528</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21149,28 +21259,28 @@
         <v>0.0114</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1295621066178235</v>
+        <v>-0.06474695759258531</v>
       </c>
       <c r="J9" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K9" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001891958514661285</v>
+        <v>0.0004604039560601736</v>
       </c>
       <c r="M9" t="n">
-        <v>16.83108419003631</v>
+        <v>17.15451616624139</v>
       </c>
       <c r="N9" t="n">
-        <v>484.5058399336079</v>
+        <v>500.6672342741655</v>
       </c>
       <c r="O9" t="n">
-        <v>22.01149335991559</v>
+        <v>22.37559461275086</v>
       </c>
       <c r="P9" t="n">
-        <v>335.4260790455842</v>
+        <v>334.7284012857733</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21221,28 +21331,28 @@
         <v>0.0157</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3878243367353805</v>
+        <v>0.5613641325990605</v>
       </c>
       <c r="J10" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K10" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01894655445239546</v>
+        <v>0.0338974956967889</v>
       </c>
       <c r="M10" t="n">
-        <v>15.16088182764903</v>
+        <v>15.65976110633746</v>
       </c>
       <c r="N10" t="n">
-        <v>426.8226420020229</v>
+        <v>494.9051383104223</v>
       </c>
       <c r="O10" t="n">
-        <v>20.65968639650716</v>
+        <v>22.24646350120446</v>
       </c>
       <c r="P10" t="n">
-        <v>290.7060989642025</v>
+        <v>288.8390639221827</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21293,28 +21403,28 @@
         <v>0.0103</v>
       </c>
       <c r="I11" t="n">
-        <v>3.658336348861045</v>
+        <v>3.624594115845101</v>
       </c>
       <c r="J11" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K11" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3298325101130591</v>
+        <v>0.3274640656299713</v>
       </c>
       <c r="M11" t="n">
-        <v>31.24585732501145</v>
+        <v>31.19913297705519</v>
       </c>
       <c r="N11" t="n">
-        <v>1465.639596262703</v>
+        <v>1462.148253250897</v>
       </c>
       <c r="O11" t="n">
-        <v>38.28367271125777</v>
+        <v>38.2380471945273</v>
       </c>
       <c r="P11" t="n">
-        <v>294.1293376659748</v>
+        <v>294.4981813726746</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21365,28 +21475,28 @@
         <v>0.0174</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1804290549097245</v>
+        <v>-0.1517184854375234</v>
       </c>
       <c r="J12" t="n">
+        <v>361</v>
+      </c>
+      <c r="K12" t="n">
         <v>359</v>
       </c>
-      <c r="K12" t="n">
-        <v>357</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.004102361302048108</v>
+        <v>0.002910344339937421</v>
       </c>
       <c r="M12" t="n">
-        <v>15.04016637971053</v>
+        <v>15.05737777059242</v>
       </c>
       <c r="N12" t="n">
-        <v>444.9548234393533</v>
+        <v>446.3817586155558</v>
       </c>
       <c r="O12" t="n">
-        <v>21.09395229537019</v>
+        <v>21.12774854582371</v>
       </c>
       <c r="P12" t="n">
-        <v>293.8023100078171</v>
+        <v>293.4993301182338</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -21424,7 +21534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M360"/>
+  <dimension ref="A1:M362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45295,25 +45405,159 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>-36.94559291615708,175.17061165110908</t>
+          <t>-36.94547932383964,175.17054434409945</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>-36.94604621194875,175.171640767646</t>
+          <t>-36.945287233789074,175.17079806413383</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>-36.94550977607033,175.1704729474884</t>
+          <t>-36.94555026312852,175.17072055458596</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>-36.94502746742775,175.17146112177625</t>
+          <t>-36.94502014885427,175.17137595620324</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>-36.947155553014,175.16581043891725</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>-36.947567885093186,175.16630429913957</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>-36.94785064470837,175.16718112588111</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>-36.947756671833766,175.16807224745506</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>-36.947596601895086,175.1688197610904</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>-36.946550662902844,175.16920937783064</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>-36.94641429413129,175.17010388104714</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>-36.94539331587196,175.1704933818378</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>-36.94508657400616,175.17057527295486</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>-36.94555163007467,175.17072891449212</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>-36.94501827843569,175.17135419042984</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>-36.94712868088998,175.1658211035412</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>-36.94743854460117,175.16629988423853</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>-36.94787591455163,175.1671844375829</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>-36.94775971885061,175.16807264317697</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>-36.947614041412876,175.1688297438845</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>-36.94637536732024,175.16910903522458</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>-36.946254890187205,175.1700094294443</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>-36.94535230544085,175.17046908199313</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>-36.94508657400616,175.17057527295486</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>-36.94551369709672,175.17049692719692</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>-36.9450171561826,175.17134113096623</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
